--- a/public/templates/Shablloni-5-Faqe.xlsx
+++ b/public/templates/Shablloni-5-Faqe.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Graniti\Junik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\AAB\Viti 3 Semestri 6\Tema-Graniti\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEBEDE8-F7D0-4D6D-9F4A-90D6233A1B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBE600F-7361-4D55-904E-C41138E18151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -260,20 +260,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Objekti-Building : </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Riorganizimi i kuzhinës në objektin - institucionin Parashkollorë dhe montimi i Platformës për personat me nevoja të veçanta </t>
-    </r>
+    <t xml:space="preserve">Objekti-Building : Riorganizimi i kuzhinës në objektin - institucionin Parashkollorë dhe montimi i Platformës për personat me nevoja të veçanta </t>
   </si>
 </sst>
 </file>
@@ -284,7 +271,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,13 +375,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -724,15 +704,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -747,6 +718,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1090,35 +1070,35 @@
         <v>7</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="62" t="s">
+      <c r="F3" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="63"/>
-      <c r="H3" s="64"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="69"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="C4" s="41"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="64"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="64"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="69"/>
     </row>
     <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="42" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="69"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="16"/>
@@ -1147,13 +1127,13 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="67"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="64"/>
       <c r="F9" s="15" t="s">
         <v>6</v>
       </c>
@@ -1163,28 +1143,28 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="65"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="67"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="64"/>
       <c r="F10" s="4"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="68" t="s">
+      <c r="H10" s="65" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="65"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="67"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="64"/>
       <c r="F11" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="68"/>
+      <c r="H11" s="65"/>
     </row>
     <row r="12" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
@@ -1194,7 +1174,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="6"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="69"/>
+      <c r="H12" s="66"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
